--- a/objects/no_heme_treatment.xlsx
+++ b/objects/no_heme_treatment.xlsx
@@ -65,43 +65,43 @@
     <t xml:space="preserve">adjustment1</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06 (1.85, 2.29)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06 (1.84, 2.31)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24 (0.99, 1.54)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72 (1.36, 2.17)</t>
+    <t xml:space="preserve">2.08 (1.86, 2.31)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09 (1.86, 2.33)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23 (0.98, 1.52)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70 (1.35, 2.14)</t>
   </si>
   <si>
     <t xml:space="preserve">adjustment2</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15 (1.91, 2.41)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19 (1.94, 2.47)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28 (1.00, 1.61)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64 (1.27, 2.10)</t>
+    <t xml:space="preserve">2.17 (1.93, 2.43)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21 (1.96, 2.50)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27 (1.00, 1.60)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63 (1.26, 2.08)</t>
   </si>
   <si>
     <t xml:space="preserve">adjustment3</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99 (1.75, 2.25)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08 (1.83, 2.36)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62 (1.25, 2.08)</t>
+    <t xml:space="preserve">2.00 (1.76, 2.26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09 (1.84, 2.37)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63 (1.26, 2.10)</t>
   </si>
   <si>
     <t xml:space="preserve">1.47 (1.12, 1.92)</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">0.64 (0.57, 0.72)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61 (0.49, 0.75)</t>
+    <t xml:space="preserve">0.61 (0.49, 0.76)</t>
   </si>
   <si>
     <t xml:space="preserve">0.90 (0.72, 1.12)</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">0.76 (0.67, 0.86)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.72 (0.63, 0.83)</t>
+    <t xml:space="preserve">0.72 (0.63, 0.82)</t>
   </si>
   <si>
     <t xml:space="preserve">0.81 (0.62, 1.04)</t>
@@ -191,40 +191,40 @@
     <t xml:space="preserve">3.59 (1.66, 6.73)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.83 (0.55, 1.19)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77 (0.50, 1.15)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61 (0.25, 1.25)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03 (0.47, 1.95)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.72 (0.44, 1.10)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.66 (0.39, 1.05)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52 (0.17, 1.18)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78 (0.29, 1.68)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78 (0.47, 1.22)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77 (0.44, 1.24)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.84 (0.28, 1.94)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.76 (0.25, 1.77)</t>
+    <t xml:space="preserve">0.82 (0.55, 1.19)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77 (0.50, 1.14)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62 (0.25, 1.25)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04 (0.47, 1.97)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.71 (0.44, 1.09)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.65 (0.38, 1.04)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52 (0.17, 1.19)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78 (0.29, 1.69)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77 (0.46, 1.20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.76 (0.44, 1.23)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83 (0.27, 1.91)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77 (0.25, 1.78)</t>
   </si>
   <si>
     <t xml:space="preserve">Surgery Only</t>
@@ -254,19 +254,19 @@
     <t xml:space="preserve">1.76 (0.49, 4.38)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47 (0.26, 0.78)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46 (0.25, 0.78)</t>
+    <t xml:space="preserve">0.48 (0.27, 0.79)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46 (0.25, 0.79)</t>
   </si>
   <si>
     <t xml:space="preserve">0.30 (0.06, 0.87)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61 (0.17, 1.52)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44 (0.23, 0.78)</t>
+    <t xml:space="preserve">0.60 (0.17, 1.52)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45 (0.23, 0.78)</t>
   </si>
   <si>
     <t xml:space="preserve">0.42 (0.20, 0.76)</t>
@@ -275,19 +275,19 @@
     <t xml:space="preserve">0.35 (0.07, 1.01)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.67 (0.19, 1.69)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52 (0.27, 0.92)</t>
+    <t xml:space="preserve">0.67 (0.18, 1.68)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.53 (0.27, 0.92)</t>
   </si>
   <si>
     <t xml:space="preserve">0.50 (0.24, 0.92)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.55 (0.11, 1.58)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79 (0.22, 2.01)</t>
+    <t xml:space="preserve">0.55 (0.12, 1.59)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79 (0.22, 2.00)</t>
   </si>
 </sst>
 </file>
